--- a/table/resources/sample/AuxiliaryAward.xlsx
+++ b/table/resources/sample/AuxiliaryAward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="AuxiliaryAward" sheetId="24" r:id="rId1"/>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -247,168 +247,6 @@
   </si>
   <si>
     <t>通赔</t>
-  </si>
-  <si>
-    <t>水果机</t>
-  </si>
-  <si>
-    <t>送灯</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1;4,1;5,1;6,1;7,1;8,1;9,1</t>
-  </si>
-  <si>
-    <t>20100001,1,1;20100002,1,1;20100003,1,1;20100004,1,1;20100005,1,1;20100006,1,1;20100007,1,1;20100008,1,1;20100009,1,1;20100010,1,1;20100011,1,1;20100012,1,1;20100013,1,1;20100014,1,1;20100015,1,1;20100016,1,1;20100017,1,1;20100018,1,1;20100019,1,1;20100020,1,1;20100021,1,1;20100022,1,1;20100023,1,1;20100024,1,1;</t>
-  </si>
-  <si>
-    <t>幸运奖</t>
-  </si>
-  <si>
-    <t>随机送灯</t>
-  </si>
-  <si>
-    <t>1,1;2,1;3,1</t>
-  </si>
-  <si>
-    <t>随机奖</t>
-  </si>
-  <si>
-    <t>小三元</t>
-  </si>
-  <si>
-    <t>3,1</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000007,1,1;201000013,1,1;201000014,1,1;201000019,1,1;</t>
-  </si>
-  <si>
-    <t>3种开奖结果，需扣除本局的开奖位置，同一下注区对应的开奖结果赔率相同算一种</t>
-  </si>
-  <si>
-    <t>大三元</t>
-  </si>
-  <si>
-    <t>20100008,1,1;20100016,1,1;20100020,1</t>
-  </si>
-  <si>
-    <t>开奖位置ID,权重</t>
-  </si>
-  <si>
-    <t>小四喜</t>
-  </si>
-  <si>
-    <t>4,1</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000005,1,1;201000007,1,1;201000011,1,1;201000013,1,1;201000014,1,1;201000017,1,1;201000019,1,1;201000023,1,1;</t>
-  </si>
-  <si>
-    <t>4种开奖结果，需扣除本局的开奖位置</t>
-  </si>
-  <si>
-    <t>大四喜</t>
-  </si>
-  <si>
-    <t>20100004,1,1;20100008,1,1;20100016,1,1;20100020,1</t>
-  </si>
-  <si>
-    <t>大满贯</t>
-  </si>
-  <si>
-    <t>7,1</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000005,1,1;201000007,1,1;201000008,1,1;201000011,1,1;201000013,1,1;201000014,1,1;201000016,1,1;201000017,1,1;201000019,1,1;201000020,1,1;201000023,1,1;</t>
-  </si>
-  <si>
-    <t>7种开奖结果，需扣除本局的开奖位置</t>
-  </si>
-  <si>
-    <t>开火车</t>
-  </si>
-  <si>
-    <t>3,1;4,1;5,1</t>
-  </si>
-  <si>
-    <t>开奖位置后面连着取3-5个</t>
-  </si>
-  <si>
-    <t>六六大顺</t>
-  </si>
-  <si>
-    <t>201000002,1,1;201000005,1,1;201000006,1,1;201000007,1,1;201000013,1,1;201000016,1,1</t>
-  </si>
-  <si>
-    <t>天龙八部</t>
-  </si>
-  <si>
-    <t>201000004,1,1;201000005,1,1;201000007,1,1;201000008,1,1;201000016,1,1;201000019,1,1;201000020,1,1;201000024,1,1;</t>
-  </si>
-  <si>
-    <t>8种开奖结果，需扣除本局的开奖位置</t>
-  </si>
-  <si>
-    <t>纵横四海</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000003,1,1;201000004,1,1;201000005,1,1;201000006,1,1;201000007,1,1;201000008,1,1;201000024,1,1;</t>
-  </si>
-  <si>
-    <t>上</t>
-  </si>
-  <si>
-    <t>201000006,1,1;201000007,1,1;201000008,1,1;201000009,1,1;201000010,1,1;201000011,1,1;201000012,1,1;201000013,1,1;201000014,1,1;</t>
-  </si>
-  <si>
-    <t>右</t>
-  </si>
-  <si>
-    <t>201000012,1,1;201000013,1,1;201000014,1,1;201000015,1,1;201000016,1,1;201000017,1,1;201000018,1,1;201000019,1,1;201000020,1,1;</t>
-  </si>
-  <si>
-    <t>下</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000018,1,1;201000019,1,1;201000020,1,1;201000021,1,1;201000022,1,1;201000023,1,1;201000024,1,1;</t>
-  </si>
-  <si>
-    <t>左</t>
-  </si>
-  <si>
-    <t>仙女散花</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000002,1,1;201000005,1,1;201000006,1,1;201000007,1,1;201000012,1,1;201000016,1,1;201000000,1,1;</t>
-  </si>
-  <si>
-    <t>九莲宝灯</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000006,1,1;201000007,1,1;201000013,1,1;201000005,1,1;201000008,1,1;201000004,1,1;201000016,1,1;201000017,1,1;</t>
-  </si>
-  <si>
-    <t>201000023,1,1;201000019,1,1;201000017,1,1;201000011,1,1;201000001,1,1;201000014,1,1</t>
-  </si>
-  <si>
-    <t>201000004,1,1;201000017,1,1;201000007,1,1;201000008,1,1;201000016,1,1;201000019,1,1;201000020,1,1;201000024,1,1;</t>
-  </si>
-  <si>
-    <t>201000004,1,1;201000023,1,1;201000007,1,1;201000008,1,1;201000016,1,1;201000019,1,1;201000020,1,1;201000024,1,1;</t>
-  </si>
-  <si>
-    <t>201000014,1,1;201000019,1,1;201000013,1,1;201000011,1,1;201000006,1,1;201000012,1,1;201000016,1,1;201000000,1,1;</t>
-  </si>
-  <si>
-    <t>201000017,1,1;201000018,1,1;201000002,1,1;201000006,1,1;201000016,1,1;201000001,1,1;201000007,1,1;201000000,1,1;</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000006,1,1;201000007,1,1;201000013,1,1;201000005,1,1;201000008,1,1;201000004,1,1;201000016,1,1;201000011,1,1;</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000006,1,1;201000019,1,1;201000013,1,1;201000017,1,1;201000008,1,1;201000004,1,1;201000016,1,1;201000011,1,1;</t>
-  </si>
-  <si>
-    <t>201000001,1,1;201000006,1,1;201000007,1,1;201000013,1,1;201000005,1,1;201000008,1,1;201000004,1,1;201000016,1,1;201000023,1,1;</t>
   </si>
 </sst>
 </file>
@@ -421,7 +259,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,12 +281,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -955,156 +787,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1136,13 +968,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1671,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1699,7 +1525,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" hidden="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" hidden="1" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1727,7 +1553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" hidden="1" spans="2:10">
+    <row r="4" s="1" customFormat="1" hidden="1" spans="1:11">
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="D4" s="2"/>
@@ -1738,7 +1564,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>200300901</v>
       </c>
@@ -1761,7 +1587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>200300902</v>
       </c>
@@ -1785,766 +1611,129 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="2">
-        <f>B7*1000+D7</f>
-        <v>201000901</v>
-      </c>
-      <c r="B7" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2">
-        <v>901</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="2">
-        <f>B8*1000+D8</f>
-        <v>201000902</v>
-      </c>
-      <c r="B8" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2">
-        <v>902</v>
-      </c>
-      <c r="E8" s="2">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="2">
-        <f>B9*1000+D9</f>
-        <v>201000903</v>
-      </c>
-      <c r="B9" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="11">
-        <v>903</v>
-      </c>
-      <c r="E9" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>36</v>
-      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="11"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="2">
-        <f>B10*1000+D10</f>
-        <v>201000904</v>
-      </c>
-      <c r="B10" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="2">
-        <v>904</v>
-      </c>
-      <c r="E10" s="2">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="2">
-        <f>B11*1000+D11</f>
-        <v>201000905</v>
-      </c>
-      <c r="B11" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="2">
-        <v>905</v>
-      </c>
-      <c r="E11" s="2">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="10" t="s">
-        <v>43</v>
-      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="2">
-        <f>B12*1000+D12</f>
-        <v>201000906</v>
-      </c>
-      <c r="B12" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="2">
-        <v>906</v>
-      </c>
-      <c r="E12" s="2">
-        <v>9</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="2">
-        <f>B13*1000+D13</f>
-        <v>201000907</v>
-      </c>
-      <c r="B13" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>907</v>
-      </c>
-      <c r="E13" s="2">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>49</v>
-      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="2">
-        <f>B14*1000+D14</f>
-        <v>201000908</v>
-      </c>
-      <c r="B14" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2">
-        <v>908</v>
-      </c>
-      <c r="E14" s="2">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>52</v>
-      </c>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="2">
-        <f>B15*1000+D15</f>
-        <v>201000909</v>
-      </c>
-      <c r="B15" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2">
-        <v>909</v>
-      </c>
-      <c r="E15" s="2">
-        <v>18</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
       <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="I15" s="10"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="2">
-        <f>B16*1000+D16</f>
-        <v>201000910</v>
-      </c>
-      <c r="B16" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="2">
-        <v>910</v>
-      </c>
-      <c r="E16" s="2">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="2">
-        <f>B17*1000+D17</f>
-        <v>201000911</v>
-      </c>
-      <c r="B17" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="2">
-        <v>911</v>
-      </c>
-      <c r="E17" s="2">
-        <v>22</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="2">
-        <f>B18*1000+D18</f>
-        <v>201000912</v>
-      </c>
-      <c r="B18" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="2">
-        <v>912</v>
-      </c>
-      <c r="E18" s="2">
-        <v>22</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="2">
-        <f>B19*1000+D19</f>
-        <v>201000913</v>
-      </c>
-      <c r="B19" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="2">
-        <v>913</v>
-      </c>
-      <c r="E19" s="2">
-        <v>22</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="2">
-        <f>B20*1000+D20</f>
-        <v>201000914</v>
-      </c>
-      <c r="B20" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2">
-        <v>914</v>
-      </c>
-      <c r="E20" s="2">
-        <v>22</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="2">
-        <f>B21*1000+D21</f>
-        <v>201000915</v>
-      </c>
-      <c r="B21" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="2">
-        <v>915</v>
-      </c>
-      <c r="E21" s="2">
-        <v>19</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
+      <c r="I16" s="10"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="8:11">
+      <c r="I17" s="10"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="8:11">
+      <c r="I18" s="10"/>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="8:11">
+      <c r="I19" s="10"/>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="8:11">
+      <c r="I20" s="10"/>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="8:11">
       <c r="H21" s="10"/>
-      <c r="I21" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="2">
-        <f>B22*1000+D22</f>
-        <v>201000916</v>
-      </c>
-      <c r="B22" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="2">
-        <v>916</v>
-      </c>
-      <c r="E22" s="2">
-        <v>21</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
+      <c r="I21" s="10"/>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="8:11">
       <c r="H22" s="10"/>
-      <c r="I22" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="2">
-        <f>B23*1000+D23</f>
-        <v>201000917</v>
-      </c>
-      <c r="B23" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="2">
-        <v>917</v>
-      </c>
-      <c r="E23" s="2">
-        <v>18</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
+      <c r="I22" s="10"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="8:11">
       <c r="H23" s="10"/>
-      <c r="I23" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="2">
-        <f>B24*1000+D24</f>
-        <v>201000918</v>
-      </c>
-      <c r="B24" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="2">
-        <v>918</v>
-      </c>
-      <c r="E24" s="2">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="2">
-        <f>B25*1000+D25</f>
-        <v>201000919</v>
-      </c>
-      <c r="B25" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="2">
-        <v>919</v>
-      </c>
-      <c r="E25" s="2">
-        <v>20</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="2">
-        <f>B26*1000+D26</f>
-        <v>201000920</v>
-      </c>
-      <c r="B26" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="2">
-        <v>920</v>
-      </c>
-      <c r="E26" s="2">
-        <v>19</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
+      <c r="I23" s="10"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="8:11">
+      <c r="I24" s="10"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="8:11">
+      <c r="I25" s="10"/>
+      <c r="K25" s="10"/>
+    </row>
+    <row r="26" spans="8:11">
       <c r="H26" s="10"/>
-      <c r="I26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="2">
-        <f>B27*1000+D27</f>
-        <v>201000921</v>
-      </c>
-      <c r="B27" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D27" s="2">
-        <v>921</v>
-      </c>
-      <c r="E27" s="2">
-        <v>19</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
+      <c r="I26" s="10"/>
+      <c r="K26" s="10"/>
+    </row>
+    <row r="27" spans="8:11">
       <c r="H27" s="10"/>
-      <c r="I27" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="2">
-        <f>B28*1000+D28</f>
-        <v>201000922</v>
-      </c>
-      <c r="B28" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="2">
-        <v>922</v>
-      </c>
-      <c r="E28" s="2">
-        <v>21</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
+      <c r="I27" s="10"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="8:11">
       <c r="H28" s="10"/>
-      <c r="I28" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="2">
-        <f>B29*1000+D29</f>
-        <v>201000923</v>
-      </c>
-      <c r="B29" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="2">
-        <v>923</v>
-      </c>
-      <c r="E29" s="2">
-        <v>21</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
+      <c r="I28" s="10"/>
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="8:11">
       <c r="H29" s="10"/>
-      <c r="I29" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="2">
-        <f>B30*1000+D30</f>
-        <v>201000924</v>
-      </c>
-      <c r="B30" s="2">
-        <v>201000</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2">
-        <v>924</v>
-      </c>
-      <c r="E30" s="2">
-        <v>21</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
+      <c r="I29" s="10"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="8:11">
       <c r="H30" s="10"/>
-      <c r="I30" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>39</v>
-      </c>
+      <c r="I30" s="10"/>
+      <c r="K30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C5:C8" calculatedColumn="1"/>
+    <ignoredError sqref="C5:C6" calculatedColumn="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
